--- a/ExcelTool/LubanTools/DataTables/Datas/ClothShopData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/ClothShopData.xlsx
@@ -1,24 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAB475F8-BAB3-44A9-9218-E64F95D67949}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1760" yWindow="10080" windowWidth="27010" windowHeight="10250" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
-    <sheet name="ClothShopData" sheetId="1" r:id="rId1"/>
+    <sheet name="布料商店" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -28,76 +30,65 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="15">
   <si>
     <t>##var</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemID</t>
+  </si>
+  <si>
+    <t>ItemNumber</t>
+  </si>
+  <si>
+    <t>Price</t>
+  </si>
+  <si>
+    <t>UpdateMode</t>
   </si>
   <si>
     <t>##type</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>long</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t xml:space="preserve">int </t>
+  </si>
+  <si>
+    <t>ShopUpdateType</t>
   </si>
   <si>
     <t>##</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>long</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ItemNumber</t>
   </si>
   <si>
     <t>ID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>物品数量</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Price</t>
-  </si>
-  <si>
-    <t xml:space="preserve">int </t>
   </si>
   <si>
     <t>价格</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>UpdateMode</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Day</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ShopUpdateType</t>
-  </si>
-  <si>
-    <t>ItemID</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -105,7 +96,6 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -113,7 +103,6 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -121,12 +110,162 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -139,13 +278,214 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="11">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -165,23 +505,250 @@
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
+        <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
-        <color auto="1"/>
+        <color rgb="FFB2B2B2"/>
       </right>
       <top style="thin">
-        <color auto="1"/>
+        <color rgb="FFB2B2B2"/>
       </top>
       <bottom style="thin">
-        <color auto="1"/>
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -190,34 +757,78 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="1" xr:uid="{4E3973F2-D0A3-4DB0-AF02-72FD7CD2A736}"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规 2" xfId="49"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -266,7 +877,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic Light"/>
@@ -301,7 +912,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic"/>
@@ -475,218 +1086,213 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:E13"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
   <cols>
-    <col min="3" max="3" width="29.1640625" customWidth="1"/>
-    <col min="4" max="4" width="27.4140625" customWidth="1"/>
-    <col min="5" max="5" width="19.33203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="29.1666666666667" customWidth="1"/>
+    <col min="4" max="4" width="27.4166666666667" customWidth="1"/>
+    <col min="5" max="5" width="19.3333333333333" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>11</v>
-      </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="6" t="s">
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" t="s">
         <v>13</v>
       </c>
+      <c r="E3" s="4" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="B4" s="4">
+    <row r="4" ht="15.5" spans="1:5">
+      <c r="B4" s="5">
         <v>220000</v>
       </c>
       <c r="C4" s="2">
         <v>5</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="6">
         <v>500</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>12</v>
+      <c r="E4" s="4" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="B5" s="4">
+    <row r="5" ht="15.5" spans="1:5">
+      <c r="B5" s="5">
         <v>220001</v>
       </c>
       <c r="C5" s="2">
         <v>5</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="6">
         <v>500</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>12</v>
+      <c r="E5" s="4" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="B6" s="4">
+    <row r="6" ht="15.5" spans="1:5">
+      <c r="B6" s="5">
         <v>220002</v>
       </c>
       <c r="C6" s="2">
         <v>5</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6" s="6">
         <v>550</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>12</v>
+      <c r="E6" s="4" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="B7" s="4">
+    <row r="7" ht="15.5" spans="1:5">
+      <c r="B7" s="5">
         <v>220003</v>
       </c>
       <c r="C7" s="2">
         <v>5</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="6">
         <v>550</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>12</v>
+      <c r="E7" s="4" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="B8" s="4">
+    <row r="8" ht="15.5" spans="1:5">
+      <c r="B8" s="5">
         <v>220004</v>
       </c>
       <c r="C8" s="2">
         <v>5</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D8" s="6">
         <v>600</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>12</v>
+      <c r="E8" s="4" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="B9" s="4">
+    <row r="9" ht="15.5" spans="1:5">
+      <c r="B9" s="5">
         <v>220005</v>
       </c>
       <c r="C9" s="2">
         <v>5</v>
       </c>
-      <c r="D9" s="5">
+      <c r="D9" s="6">
         <v>600</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>12</v>
+      <c r="E9" s="4" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="B10" s="4">
+    <row r="10" ht="15.5" spans="1:5">
+      <c r="B10" s="5">
         <v>220006</v>
       </c>
       <c r="C10" s="2">
         <v>5</v>
       </c>
-      <c r="D10" s="5">
+      <c r="D10" s="6">
         <v>650</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>12</v>
+      <c r="E10" s="4" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="B11" s="4">
+    <row r="11" ht="15.5" spans="1:5">
+      <c r="B11" s="5">
         <v>220007</v>
       </c>
       <c r="C11" s="2">
         <v>5</v>
       </c>
-      <c r="D11" s="5">
+      <c r="D11" s="6">
         <v>650</v>
       </c>
-      <c r="E11" s="3" t="s">
-        <v>12</v>
+      <c r="E11" s="4" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="B12" s="4">
+    <row r="12" ht="15.5" spans="1:5">
+      <c r="B12" s="5">
         <v>220008</v>
       </c>
       <c r="C12" s="2">
         <v>5</v>
       </c>
-      <c r="D12" s="5">
+      <c r="D12" s="6">
         <v>700</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>12</v>
+      <c r="E12" s="4" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="B13" s="4">
+    <row r="13" ht="15.5" spans="1:5">
+      <c r="B13" s="5">
         <v>220009</v>
       </c>
       <c r="C13" s="2">
         <v>5</v>
       </c>
-      <c r="D13" s="5">
+      <c r="D13" s="6">
         <v>700</v>
       </c>
-      <c r="E13" s="3" t="s">
-        <v>12</v>
+      <c r="E13" s="4" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/ExcelTool/LubanTools/DataTables/Datas/ClothShopData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/ClothShopData.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E422F00F-90DE-4514-99D7-EE0B083480F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-2140" yWindow="5560" windowWidth="42470" windowHeight="15800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="布料商店" sheetId="1" r:id="rId1"/>
@@ -33,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="18">
   <si>
     <t>##var</t>
   </si>
@@ -50,6 +44,9 @@
     <t>UpdateMode</t>
   </si>
   <si>
+    <t>BuyLimit</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -77,72 +74,185 @@
     <t>价格</t>
   </si>
   <si>
+    <t>刷新模式</t>
+  </si>
+  <si>
+    <t>购买上限</t>
+  </si>
+  <si>
     <t>Day</t>
-  </si>
-  <si>
-    <t>BuyLimit</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>购买上限</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>刷新模式</t>
-    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="等线"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="等线"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -151,12 +261,192 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -166,80 +456,321 @@
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
+        <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
-        <color auto="1"/>
+        <color rgb="FFB2B2B2"/>
       </right>
       <top style="thin">
-        <color auto="1"/>
+        <color rgb="FFB2B2B2"/>
       </top>
       <bottom style="thin">
-        <color auto="1"/>
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFDEE0E3"/>
+        <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
-        <color rgb="FFDEE0E3"/>
+        <color rgb="FF7F7F7F"/>
       </right>
       <top style="thin">
-        <color rgb="FFDEE0E3"/>
+        <color rgb="FF7F7F7F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFDEE0E3"/>
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规 2" xfId="49"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -497,253 +1028,255 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:F13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="5"/>
   <cols>
-    <col min="3" max="3" width="29.1640625" customWidth="1"/>
-    <col min="4" max="4" width="27.4140625" customWidth="1"/>
-    <col min="5" max="5" width="19.33203125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="9" style="1"/>
+    <col min="1" max="2" width="9" style="1"/>
+    <col min="3" max="3" width="29.1666666666667" style="1" customWidth="1"/>
+    <col min="4" max="4" width="27.4166666666667" style="1" customWidth="1"/>
+    <col min="5" max="5" width="19.3333333333333" style="2" customWidth="1"/>
+    <col min="6" max="6" width="9" style="2"/>
+    <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:6">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>15</v>
       </c>
+      <c r="F3" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="4" spans="1:6">
+      <c r="B4" s="1">
+        <v>220000</v>
+      </c>
+      <c r="C4" s="1">
+        <v>1</v>
+      </c>
+      <c r="D4" s="1">
+        <v>200</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="1">
         <v>5</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>16</v>
-      </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" s="6" t="s">
+    <row r="5" spans="1:6">
+      <c r="B5" s="1">
+        <v>220001</v>
+      </c>
+      <c r="C5" s="1">
+        <v>1</v>
+      </c>
+      <c r="D5" s="1">
+        <v>200</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>17</v>
       </c>
+      <c r="F5" s="1">
+        <v>5</v>
+      </c>
     </row>
-    <row r="4" spans="1:6" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="B4" s="4">
-        <v>220000</v>
-      </c>
-      <c r="C4" s="2">
+    <row r="6" spans="1:6">
+      <c r="B6" s="1">
+        <v>220002</v>
+      </c>
+      <c r="C6" s="1">
+        <v>1</v>
+      </c>
+      <c r="D6" s="1">
+        <v>400</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" s="1">
         <v>5</v>
       </c>
-      <c r="D4" s="5">
-        <v>500</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" s="1">
-        <v>10</v>
-      </c>
     </row>
-    <row r="5" spans="1:6" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="B5" s="4">
-        <v>220001</v>
-      </c>
-      <c r="C5" s="2">
+    <row r="7" spans="1:6">
+      <c r="B7" s="1">
+        <v>220003</v>
+      </c>
+      <c r="C7" s="1">
+        <v>1</v>
+      </c>
+      <c r="D7" s="1">
+        <v>400</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" s="1">
         <v>5</v>
       </c>
-      <c r="D5" s="5">
-        <v>500</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" s="1">
-        <v>10</v>
-      </c>
     </row>
-    <row r="6" spans="1:6" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="B6" s="4">
-        <v>220002</v>
-      </c>
-      <c r="C6" s="2">
+    <row r="8" spans="1:6">
+      <c r="B8" s="1">
+        <v>220004</v>
+      </c>
+      <c r="C8" s="1">
+        <v>1</v>
+      </c>
+      <c r="D8" s="1">
+        <v>600</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8" s="1">
         <v>5</v>
       </c>
-      <c r="D6" s="5">
-        <v>550</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" s="1">
-        <v>10</v>
-      </c>
     </row>
-    <row r="7" spans="1:6" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="B7" s="4">
-        <v>220003</v>
-      </c>
-      <c r="C7" s="2">
+    <row r="9" spans="1:6">
+      <c r="B9" s="1">
+        <v>220005</v>
+      </c>
+      <c r="C9" s="1">
+        <v>1</v>
+      </c>
+      <c r="D9" s="1">
+        <v>600</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F9" s="1">
         <v>5</v>
       </c>
-      <c r="D7" s="5">
-        <v>550</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7" s="1">
-        <v>10</v>
-      </c>
     </row>
-    <row r="8" spans="1:6" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="B8" s="4">
-        <v>220004</v>
-      </c>
-      <c r="C8" s="2">
+    <row r="10" spans="1:6">
+      <c r="B10" s="1">
+        <v>220006</v>
+      </c>
+      <c r="C10" s="1">
+        <v>1</v>
+      </c>
+      <c r="D10" s="1">
+        <v>800</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F10" s="1">
         <v>5</v>
       </c>
-      <c r="D8" s="5">
-        <v>600</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F8" s="1">
-        <v>10</v>
-      </c>
     </row>
-    <row r="9" spans="1:6" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="B9" s="4">
-        <v>220005</v>
-      </c>
-      <c r="C9" s="2">
+    <row r="11" spans="1:6">
+      <c r="B11" s="1">
+        <v>220007</v>
+      </c>
+      <c r="C11" s="1">
+        <v>1</v>
+      </c>
+      <c r="D11" s="1">
+        <v>800</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11" s="1">
         <v>5</v>
       </c>
-      <c r="D9" s="5">
-        <v>600</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F9" s="1">
-        <v>10</v>
-      </c>
     </row>
-    <row r="10" spans="1:6" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="B10" s="4">
-        <v>220006</v>
-      </c>
-      <c r="C10" s="2">
+    <row r="12" spans="1:6">
+      <c r="B12" s="1">
+        <v>220008</v>
+      </c>
+      <c r="C12" s="1">
+        <v>1</v>
+      </c>
+      <c r="D12" s="1">
+        <v>1000</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F12" s="1">
         <v>5</v>
       </c>
-      <c r="D10" s="5">
-        <v>650</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F10" s="1">
-        <v>10</v>
-      </c>
     </row>
-    <row r="11" spans="1:6" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="B11" s="4">
-        <v>220007</v>
-      </c>
-      <c r="C11" s="2">
+    <row r="13" spans="1:6">
+      <c r="B13" s="1">
+        <v>220009</v>
+      </c>
+      <c r="C13" s="1">
+        <v>1</v>
+      </c>
+      <c r="D13" s="1">
+        <v>1000</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F13" s="1">
         <v>5</v>
-      </c>
-      <c r="D11" s="5">
-        <v>650</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F11" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="B12" s="4">
-        <v>220008</v>
-      </c>
-      <c r="C12" s="2">
-        <v>5</v>
-      </c>
-      <c r="D12" s="5">
-        <v>700</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F12" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="B13" s="4">
-        <v>220009</v>
-      </c>
-      <c r="C13" s="2">
-        <v>5</v>
-      </c>
-      <c r="D13" s="5">
-        <v>700</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F13" s="1">
-        <v>10</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/ExcelTool/LubanTools/DataTables/Datas/ClothShopData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/ClothShopData.xlsx
@@ -703,14 +703,8 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1040,68 +1034,67 @@
     <col min="1" max="2" width="9" style="1"/>
     <col min="3" max="3" width="29.1666666666667" style="1" customWidth="1"/>
     <col min="4" max="4" width="27.4166666666667" style="1" customWidth="1"/>
-    <col min="5" max="5" width="19.3333333333333" style="2" customWidth="1"/>
-    <col min="6" max="6" width="9" style="2"/>
-    <col min="7" max="16384" width="9" style="1"/>
+    <col min="5" max="5" width="19.3333333333333" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="1" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1110,12 +1103,12 @@
         <v>220000</v>
       </c>
       <c r="C4" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D4" s="1">
         <v>200</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="1" t="s">
         <v>17</v>
       </c>
       <c r="F4" s="1">
@@ -1127,12 +1120,12 @@
         <v>220001</v>
       </c>
       <c r="C5" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D5" s="1">
         <v>200</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="1" t="s">
         <v>17</v>
       </c>
       <c r="F5" s="1">
@@ -1144,12 +1137,12 @@
         <v>220002</v>
       </c>
       <c r="C6" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D6" s="1">
         <v>400</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="1" t="s">
         <v>17</v>
       </c>
       <c r="F6" s="1">
@@ -1161,12 +1154,12 @@
         <v>220003</v>
       </c>
       <c r="C7" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D7" s="1">
         <v>400</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="1" t="s">
         <v>17</v>
       </c>
       <c r="F7" s="1">
@@ -1178,12 +1171,12 @@
         <v>220004</v>
       </c>
       <c r="C8" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D8" s="1">
         <v>600</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E8" s="1" t="s">
         <v>17</v>
       </c>
       <c r="F8" s="1">
@@ -1195,12 +1188,12 @@
         <v>220005</v>
       </c>
       <c r="C9" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D9" s="1">
         <v>600</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="1" t="s">
         <v>17</v>
       </c>
       <c r="F9" s="1">
@@ -1212,12 +1205,12 @@
         <v>220006</v>
       </c>
       <c r="C10" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D10" s="1">
         <v>800</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="E10" s="1" t="s">
         <v>17</v>
       </c>
       <c r="F10" s="1">
@@ -1229,12 +1222,12 @@
         <v>220007</v>
       </c>
       <c r="C11" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D11" s="1">
         <v>800</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="E11" s="1" t="s">
         <v>17</v>
       </c>
       <c r="F11" s="1">
@@ -1246,12 +1239,12 @@
         <v>220008</v>
       </c>
       <c r="C12" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D12" s="1">
         <v>1000</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="E12" s="1" t="s">
         <v>17</v>
       </c>
       <c r="F12" s="1">
@@ -1263,12 +1256,12 @@
         <v>220009</v>
       </c>
       <c r="C13" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D13" s="1">
         <v>1000</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="E13" s="1" t="s">
         <v>17</v>
       </c>
       <c r="F13" s="1">

--- a/ExcelTool/LubanTools/DataTables/Datas/ClothShopData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/ClothShopData.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="21">
   <si>
     <t>##var</t>
   </si>
@@ -47,6 +47,9 @@
     <t>BuyLimit</t>
   </si>
   <si>
+    <t>ShopHelpIconName</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -60,6 +63,9 @@
   </si>
   <si>
     <t>ShopUpdateType</t>
+  </si>
+  <si>
+    <t>str</t>
   </si>
   <si>
     <t>##</t>
@@ -80,6 +86,9 @@
     <t>购买上限</t>
   </si>
   <si>
+    <t>商店帮忙图标名</t>
+  </si>
+  <si>
     <t>Day</t>
   </si>
 </sst>
@@ -93,7 +102,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -104,6 +113,12 @@
     <font>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -570,142 +585,149 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1028,8 +1050,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="5"/>
+  <dimension ref="A1:G53"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
     <col min="3" max="3" width="29.1666666666667" style="1" customWidth="1"/>
@@ -1038,7 +1060,7 @@
     <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1057,48 +1079,57 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+      <c r="G2" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+        <v>18</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="B4" s="1">
         <v>220000</v>
       </c>
@@ -1109,13 +1140,17 @@
         <v>200</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F4" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
+      <c r="G4" s="1" t="str">
+        <f t="shared" ref="G4:G53" si="0">CONCATENATE(_xlfn.SINGLE(B:B),"Name.png")</f>
+        <v>220000Name.png</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="B5" s="1">
         <v>220001</v>
       </c>
@@ -1126,13 +1161,17 @@
         <v>200</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F5" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="6" spans="1:6">
+      <c r="G5" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>220001Name.png</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="B6" s="1">
         <v>220002</v>
       </c>
@@ -1143,13 +1182,17 @@
         <v>400</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F6" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:6">
+      <c r="G6" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>220002Name.png</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="B7" s="1">
         <v>220003</v>
       </c>
@@ -1160,13 +1203,17 @@
         <v>400</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F7" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="8" spans="1:6">
+      <c r="G7" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>220003Name.png</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="B8" s="1">
         <v>220004</v>
       </c>
@@ -1177,13 +1224,17 @@
         <v>600</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F8" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="9" spans="1:6">
+      <c r="G8" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>220004Name.png</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="B9" s="1">
         <v>220005</v>
       </c>
@@ -1194,13 +1245,17 @@
         <v>600</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F9" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:6">
+      <c r="G9" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>220005Name.png</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="B10" s="1">
         <v>220006</v>
       </c>
@@ -1211,13 +1266,17 @@
         <v>800</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F10" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:6">
+      <c r="G10" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>220006Name.png</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="B11" s="1">
         <v>220007</v>
       </c>
@@ -1228,13 +1287,17 @@
         <v>800</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F11" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="12" spans="1:6">
+      <c r="G11" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>220007Name.png</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
       <c r="B12" s="1">
         <v>220008</v>
       </c>
@@ -1245,13 +1308,17 @@
         <v>1000</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F12" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:6">
+      <c r="G12" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>220008Name.png</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
       <c r="B13" s="1">
         <v>220009</v>
       </c>
@@ -1262,10 +1329,854 @@
         <v>1000</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F13" s="1">
         <v>5</v>
+      </c>
+      <c r="G13" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>220009Name.png</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="B14" s="4">
+        <v>230000</v>
+      </c>
+      <c r="C14" s="1">
+        <v>5</v>
+      </c>
+      <c r="D14" s="1">
+        <v>100</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F14" s="1">
+        <v>100</v>
+      </c>
+      <c r="G14" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>230000Name.png</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="B15" s="4">
+        <v>230001</v>
+      </c>
+      <c r="C15" s="1">
+        <v>5</v>
+      </c>
+      <c r="D15" s="1">
+        <v>100</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F15" s="1">
+        <v>100</v>
+      </c>
+      <c r="G15" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>230001Name.png</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="B16" s="4">
+        <v>230002</v>
+      </c>
+      <c r="C16" s="1">
+        <v>5</v>
+      </c>
+      <c r="D16" s="1">
+        <v>100</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F16" s="1">
+        <v>100</v>
+      </c>
+      <c r="G16" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>230002Name.png</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7">
+      <c r="B17" s="4">
+        <v>230003</v>
+      </c>
+      <c r="C17" s="1">
+        <v>5</v>
+      </c>
+      <c r="D17" s="1">
+        <v>100</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F17" s="1">
+        <v>100</v>
+      </c>
+      <c r="G17" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>230003Name.png</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7">
+      <c r="B18" s="4">
+        <v>230004</v>
+      </c>
+      <c r="C18" s="1">
+        <v>5</v>
+      </c>
+      <c r="D18" s="1">
+        <v>100</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F18" s="1">
+        <v>100</v>
+      </c>
+      <c r="G18" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>230004Name.png</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7">
+      <c r="B19" s="4">
+        <v>230005</v>
+      </c>
+      <c r="C19" s="1">
+        <v>5</v>
+      </c>
+      <c r="D19" s="1">
+        <v>100</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F19" s="1">
+        <v>100</v>
+      </c>
+      <c r="G19" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>230005Name.png</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7">
+      <c r="B20" s="4">
+        <v>230006</v>
+      </c>
+      <c r="C20" s="1">
+        <v>5</v>
+      </c>
+      <c r="D20" s="1">
+        <v>100</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F20" s="1">
+        <v>100</v>
+      </c>
+      <c r="G20" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>230006Name.png</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7">
+      <c r="B21" s="4">
+        <v>230007</v>
+      </c>
+      <c r="C21" s="1">
+        <v>5</v>
+      </c>
+      <c r="D21" s="1">
+        <v>100</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F21" s="1">
+        <v>100</v>
+      </c>
+      <c r="G21" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>230007Name.png</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7">
+      <c r="B22" s="4">
+        <v>230008</v>
+      </c>
+      <c r="C22" s="1">
+        <v>5</v>
+      </c>
+      <c r="D22" s="1">
+        <v>100</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F22" s="1">
+        <v>100</v>
+      </c>
+      <c r="G22" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>230008Name.png</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7">
+      <c r="B23" s="4">
+        <v>230009</v>
+      </c>
+      <c r="C23" s="1">
+        <v>5</v>
+      </c>
+      <c r="D23" s="1">
+        <v>100</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F23" s="1">
+        <v>100</v>
+      </c>
+      <c r="G23" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>230009Name.png</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7">
+      <c r="B24" s="4">
+        <v>230010</v>
+      </c>
+      <c r="C24" s="1">
+        <v>5</v>
+      </c>
+      <c r="D24" s="1">
+        <v>100</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F24" s="1">
+        <v>100</v>
+      </c>
+      <c r="G24" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>230010Name.png</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7">
+      <c r="B25" s="4">
+        <v>230011</v>
+      </c>
+      <c r="C25" s="1">
+        <v>5</v>
+      </c>
+      <c r="D25" s="1">
+        <v>100</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F25" s="1">
+        <v>100</v>
+      </c>
+      <c r="G25" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>230011Name.png</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7">
+      <c r="B26" s="4">
+        <v>230012</v>
+      </c>
+      <c r="C26" s="1">
+        <v>5</v>
+      </c>
+      <c r="D26" s="1">
+        <v>100</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F26" s="1">
+        <v>100</v>
+      </c>
+      <c r="G26" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>230012Name.png</v>
+      </c>
+    </row>
+    <row r="27" spans="2:7">
+      <c r="B27" s="4">
+        <v>230013</v>
+      </c>
+      <c r="C27" s="1">
+        <v>5</v>
+      </c>
+      <c r="D27" s="1">
+        <v>100</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F27" s="1">
+        <v>100</v>
+      </c>
+      <c r="G27" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>230013Name.png</v>
+      </c>
+    </row>
+    <row r="28" spans="2:7">
+      <c r="B28" s="4">
+        <v>230014</v>
+      </c>
+      <c r="C28" s="1">
+        <v>5</v>
+      </c>
+      <c r="D28" s="1">
+        <v>100</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F28" s="1">
+        <v>100</v>
+      </c>
+      <c r="G28" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>230014Name.png</v>
+      </c>
+    </row>
+    <row r="29" spans="2:7">
+      <c r="B29" s="4">
+        <v>230015</v>
+      </c>
+      <c r="C29" s="1">
+        <v>5</v>
+      </c>
+      <c r="D29" s="1">
+        <v>100</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F29" s="1">
+        <v>100</v>
+      </c>
+      <c r="G29" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>230015Name.png</v>
+      </c>
+    </row>
+    <row r="30" spans="2:7">
+      <c r="B30" s="4">
+        <v>230016</v>
+      </c>
+      <c r="C30" s="1">
+        <v>5</v>
+      </c>
+      <c r="D30" s="1">
+        <v>100</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F30" s="1">
+        <v>100</v>
+      </c>
+      <c r="G30" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>230016Name.png</v>
+      </c>
+    </row>
+    <row r="31" spans="2:7">
+      <c r="B31" s="4">
+        <v>230017</v>
+      </c>
+      <c r="C31" s="1">
+        <v>5</v>
+      </c>
+      <c r="D31" s="1">
+        <v>100</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F31" s="1">
+        <v>100</v>
+      </c>
+      <c r="G31" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>230017Name.png</v>
+      </c>
+    </row>
+    <row r="32" spans="2:7">
+      <c r="B32" s="4">
+        <v>230018</v>
+      </c>
+      <c r="C32" s="1">
+        <v>5</v>
+      </c>
+      <c r="D32" s="1">
+        <v>100</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F32" s="1">
+        <v>100</v>
+      </c>
+      <c r="G32" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>230018Name.png</v>
+      </c>
+    </row>
+    <row r="33" spans="2:7">
+      <c r="B33" s="4">
+        <v>230019</v>
+      </c>
+      <c r="C33" s="1">
+        <v>5</v>
+      </c>
+      <c r="D33" s="1">
+        <v>100</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F33" s="1">
+        <v>100</v>
+      </c>
+      <c r="G33" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>230019Name.png</v>
+      </c>
+    </row>
+    <row r="34" spans="2:7">
+      <c r="B34" s="4">
+        <v>240000</v>
+      </c>
+      <c r="C34" s="1">
+        <v>5</v>
+      </c>
+      <c r="D34" s="1">
+        <v>100</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F34" s="1">
+        <v>100</v>
+      </c>
+      <c r="G34" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>240000Name.png</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7">
+      <c r="B35" s="4">
+        <v>240001</v>
+      </c>
+      <c r="C35" s="1">
+        <v>5</v>
+      </c>
+      <c r="D35" s="1">
+        <v>100</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F35" s="1">
+        <v>100</v>
+      </c>
+      <c r="G35" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>240001Name.png</v>
+      </c>
+    </row>
+    <row r="36" spans="2:7">
+      <c r="B36" s="4">
+        <v>240002</v>
+      </c>
+      <c r="C36" s="1">
+        <v>5</v>
+      </c>
+      <c r="D36" s="1">
+        <v>100</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F36" s="1">
+        <v>100</v>
+      </c>
+      <c r="G36" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>240002Name.png</v>
+      </c>
+    </row>
+    <row r="37" spans="2:7">
+      <c r="B37" s="4">
+        <v>240003</v>
+      </c>
+      <c r="C37" s="1">
+        <v>5</v>
+      </c>
+      <c r="D37" s="1">
+        <v>100</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F37" s="1">
+        <v>100</v>
+      </c>
+      <c r="G37" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>240003Name.png</v>
+      </c>
+    </row>
+    <row r="38" spans="2:7">
+      <c r="B38" s="4">
+        <v>240004</v>
+      </c>
+      <c r="C38" s="1">
+        <v>5</v>
+      </c>
+      <c r="D38" s="1">
+        <v>100</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F38" s="1">
+        <v>100</v>
+      </c>
+      <c r="G38" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>240004Name.png</v>
+      </c>
+    </row>
+    <row r="39" spans="2:7">
+      <c r="B39" s="4">
+        <v>240005</v>
+      </c>
+      <c r="C39" s="1">
+        <v>5</v>
+      </c>
+      <c r="D39" s="1">
+        <v>100</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F39" s="1">
+        <v>100</v>
+      </c>
+      <c r="G39" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>240005Name.png</v>
+      </c>
+    </row>
+    <row r="40" spans="2:7">
+      <c r="B40" s="4">
+        <v>240006</v>
+      </c>
+      <c r="C40" s="1">
+        <v>5</v>
+      </c>
+      <c r="D40" s="1">
+        <v>100</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F40" s="1">
+        <v>100</v>
+      </c>
+      <c r="G40" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>240006Name.png</v>
+      </c>
+    </row>
+    <row r="41" spans="2:7">
+      <c r="B41" s="4">
+        <v>240007</v>
+      </c>
+      <c r="C41" s="1">
+        <v>5</v>
+      </c>
+      <c r="D41" s="1">
+        <v>100</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F41" s="1">
+        <v>100</v>
+      </c>
+      <c r="G41" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>240007Name.png</v>
+      </c>
+    </row>
+    <row r="42" spans="2:7">
+      <c r="B42" s="4">
+        <v>240008</v>
+      </c>
+      <c r="C42" s="1">
+        <v>5</v>
+      </c>
+      <c r="D42" s="1">
+        <v>100</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F42" s="1">
+        <v>100</v>
+      </c>
+      <c r="G42" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>240008Name.png</v>
+      </c>
+    </row>
+    <row r="43" spans="2:7">
+      <c r="B43" s="4">
+        <v>240009</v>
+      </c>
+      <c r="C43" s="1">
+        <v>5</v>
+      </c>
+      <c r="D43" s="1">
+        <v>100</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F43" s="1">
+        <v>100</v>
+      </c>
+      <c r="G43" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>240009Name.png</v>
+      </c>
+    </row>
+    <row r="44" spans="2:7">
+      <c r="B44" s="4">
+        <v>240010</v>
+      </c>
+      <c r="C44" s="1">
+        <v>5</v>
+      </c>
+      <c r="D44" s="1">
+        <v>100</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F44" s="1">
+        <v>100</v>
+      </c>
+      <c r="G44" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>240010Name.png</v>
+      </c>
+    </row>
+    <row r="45" spans="2:7">
+      <c r="B45" s="4">
+        <v>240011</v>
+      </c>
+      <c r="C45" s="1">
+        <v>5</v>
+      </c>
+      <c r="D45" s="1">
+        <v>100</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F45" s="1">
+        <v>100</v>
+      </c>
+      <c r="G45" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>240011Name.png</v>
+      </c>
+    </row>
+    <row r="46" spans="2:7">
+      <c r="B46" s="4">
+        <v>240012</v>
+      </c>
+      <c r="C46" s="1">
+        <v>5</v>
+      </c>
+      <c r="D46" s="1">
+        <v>100</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F46" s="1">
+        <v>100</v>
+      </c>
+      <c r="G46" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>240012Name.png</v>
+      </c>
+    </row>
+    <row r="47" spans="2:7">
+      <c r="B47" s="4">
+        <v>240013</v>
+      </c>
+      <c r="C47" s="1">
+        <v>5</v>
+      </c>
+      <c r="D47" s="1">
+        <v>100</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F47" s="1">
+        <v>100</v>
+      </c>
+      <c r="G47" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>240013Name.png</v>
+      </c>
+    </row>
+    <row r="48" spans="2:7">
+      <c r="B48" s="4">
+        <v>240014</v>
+      </c>
+      <c r="C48" s="1">
+        <v>5</v>
+      </c>
+      <c r="D48" s="1">
+        <v>100</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F48" s="1">
+        <v>100</v>
+      </c>
+      <c r="G48" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>240014Name.png</v>
+      </c>
+    </row>
+    <row r="49" spans="2:7">
+      <c r="B49" s="4">
+        <v>240015</v>
+      </c>
+      <c r="C49" s="1">
+        <v>5</v>
+      </c>
+      <c r="D49" s="1">
+        <v>100</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F49" s="1">
+        <v>100</v>
+      </c>
+      <c r="G49" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>240015Name.png</v>
+      </c>
+    </row>
+    <row r="50" spans="2:7">
+      <c r="B50" s="4">
+        <v>240016</v>
+      </c>
+      <c r="C50" s="1">
+        <v>5</v>
+      </c>
+      <c r="D50" s="1">
+        <v>100</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F50" s="1">
+        <v>100</v>
+      </c>
+      <c r="G50" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>240016Name.png</v>
+      </c>
+    </row>
+    <row r="51" spans="2:7">
+      <c r="B51" s="4">
+        <v>240017</v>
+      </c>
+      <c r="C51" s="1">
+        <v>5</v>
+      </c>
+      <c r="D51" s="1">
+        <v>100</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F51" s="1">
+        <v>100</v>
+      </c>
+      <c r="G51" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>240017Name.png</v>
+      </c>
+    </row>
+    <row r="52" spans="2:7">
+      <c r="B52" s="4">
+        <v>240018</v>
+      </c>
+      <c r="C52" s="1">
+        <v>5</v>
+      </c>
+      <c r="D52" s="1">
+        <v>100</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F52" s="1">
+        <v>100</v>
+      </c>
+      <c r="G52" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>240018Name.png</v>
+      </c>
+    </row>
+    <row r="53" spans="2:7">
+      <c r="B53" s="4">
+        <v>240019</v>
+      </c>
+      <c r="C53" s="1">
+        <v>5</v>
+      </c>
+      <c r="D53" s="1">
+        <v>100</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F53" s="1">
+        <v>100</v>
+      </c>
+      <c r="G53" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>240019Name.png</v>
       </c>
     </row>
   </sheetData>

--- a/ExcelTool/LubanTools/DataTables/Datas/ClothShopData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/ClothShopData.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="18">
   <si>
     <t>##var</t>
   </si>
@@ -47,9 +47,6 @@
     <t>BuyLimit</t>
   </si>
   <si>
-    <t>ShopHelpIconName</t>
-  </si>
-  <si>
     <t>##type</t>
   </si>
   <si>
@@ -63,9 +60,6 @@
   </si>
   <si>
     <t>ShopUpdateType</t>
-  </si>
-  <si>
-    <t>str</t>
   </si>
   <si>
     <t>##</t>
@@ -84,9 +78,6 @@
   </si>
   <si>
     <t>购买上限</t>
-  </si>
-  <si>
-    <t>商店帮忙图标名</t>
   </si>
   <si>
     <t>Day</t>
@@ -718,15 +709,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1050,17 +1037,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G53"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="6"/>
+  <dimension ref="A1:F53"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
     <col min="3" max="3" width="29.1666666666667" style="1" customWidth="1"/>
     <col min="4" max="4" width="27.4166666666667" style="1" customWidth="1"/>
     <col min="5" max="5" width="19.3333333333333" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="1"/>
+    <col min="6" max="6" width="9" style="1"/>
+    <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1079,57 +1067,48 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" s="3" t="s">
+      <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+    </row>
+    <row r="4" spans="1:6">
       <c r="B4" s="1">
         <v>220000</v>
       </c>
@@ -1140,17 +1119,13 @@
         <v>200</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F4" s="1">
         <v>5</v>
       </c>
-      <c r="G4" s="1" t="str">
-        <f t="shared" ref="G4:G53" si="0">CONCATENATE(_xlfn.SINGLE(B:B),"Name.png")</f>
-        <v>220000Name.png</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+    </row>
+    <row r="5" spans="1:6">
       <c r="B5" s="1">
         <v>220001</v>
       </c>
@@ -1161,17 +1136,13 @@
         <v>200</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F5" s="1">
         <v>5</v>
       </c>
-      <c r="G5" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>220001Name.png</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+    </row>
+    <row r="6" spans="1:6">
       <c r="B6" s="1">
         <v>220002</v>
       </c>
@@ -1182,17 +1153,13 @@
         <v>400</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F6" s="1">
         <v>5</v>
       </c>
-      <c r="G6" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>220002Name.png</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+    </row>
+    <row r="7" spans="1:6">
       <c r="B7" s="1">
         <v>220003</v>
       </c>
@@ -1203,17 +1170,13 @@
         <v>400</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F7" s="1">
         <v>5</v>
       </c>
-      <c r="G7" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>220003Name.png</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+    </row>
+    <row r="8" spans="1:6">
       <c r="B8" s="1">
         <v>220004</v>
       </c>
@@ -1224,17 +1187,13 @@
         <v>600</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F8" s="1">
         <v>5</v>
       </c>
-      <c r="G8" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>220004Name.png</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+    </row>
+    <row r="9" spans="1:6">
       <c r="B9" s="1">
         <v>220005</v>
       </c>
@@ -1245,17 +1204,13 @@
         <v>600</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F9" s="1">
         <v>5</v>
       </c>
-      <c r="G9" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>220005Name.png</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
+    </row>
+    <row r="10" spans="1:6">
       <c r="B10" s="1">
         <v>220006</v>
       </c>
@@ -1266,17 +1221,13 @@
         <v>800</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F10" s="1">
         <v>5</v>
       </c>
-      <c r="G10" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>220006Name.png</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
+    </row>
+    <row r="11" spans="1:6">
       <c r="B11" s="1">
         <v>220007</v>
       </c>
@@ -1287,17 +1238,13 @@
         <v>800</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F11" s="1">
         <v>5</v>
       </c>
-      <c r="G11" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>220007Name.png</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
+    </row>
+    <row r="12" spans="1:6">
       <c r="B12" s="1">
         <v>220008</v>
       </c>
@@ -1308,17 +1255,13 @@
         <v>1000</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F12" s="1">
         <v>5</v>
       </c>
-      <c r="G12" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>220008Name.png</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
+    </row>
+    <row r="13" spans="1:6">
       <c r="B13" s="1">
         <v>220009</v>
       </c>
@@ -1329,18 +1272,14 @@
         <v>1000</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F13" s="1">
         <v>5</v>
       </c>
-      <c r="G13" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>220009Name.png</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="B14" s="4">
+    </row>
+    <row r="14" spans="1:6">
+      <c r="B14" s="2">
         <v>230000</v>
       </c>
       <c r="C14" s="1">
@@ -1350,18 +1289,14 @@
         <v>100</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F14" s="1">
         <v>100</v>
       </c>
-      <c r="G14" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>230000Name.png</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="B15" s="4">
+    </row>
+    <row r="15" spans="1:6">
+      <c r="B15" s="2">
         <v>230001</v>
       </c>
       <c r="C15" s="1">
@@ -1371,18 +1306,14 @@
         <v>100</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F15" s="1">
         <v>100</v>
       </c>
-      <c r="G15" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>230001Name.png</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="B16" s="4">
+    </row>
+    <row r="16" spans="1:6">
+      <c r="B16" s="2">
         <v>230002</v>
       </c>
       <c r="C16" s="1">
@@ -1392,18 +1323,14 @@
         <v>100</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F16" s="1">
         <v>100</v>
       </c>
-      <c r="G16" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>230002Name.png</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7">
-      <c r="B17" s="4">
+    </row>
+    <row r="17" spans="2:6">
+      <c r="B17" s="2">
         <v>230003</v>
       </c>
       <c r="C17" s="1">
@@ -1413,18 +1340,14 @@
         <v>100</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F17" s="1">
         <v>100</v>
       </c>
-      <c r="G17" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>230003Name.png</v>
-      </c>
-    </row>
-    <row r="18" spans="2:7">
-      <c r="B18" s="4">
+    </row>
+    <row r="18" spans="2:6">
+      <c r="B18" s="2">
         <v>230004</v>
       </c>
       <c r="C18" s="1">
@@ -1434,18 +1357,14 @@
         <v>100</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F18" s="1">
         <v>100</v>
       </c>
-      <c r="G18" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>230004Name.png</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7">
-      <c r="B19" s="4">
+    </row>
+    <row r="19" spans="2:6">
+      <c r="B19" s="2">
         <v>230005</v>
       </c>
       <c r="C19" s="1">
@@ -1455,18 +1374,14 @@
         <v>100</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F19" s="1">
         <v>100</v>
       </c>
-      <c r="G19" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>230005Name.png</v>
-      </c>
-    </row>
-    <row r="20" spans="2:7">
-      <c r="B20" s="4">
+    </row>
+    <row r="20" spans="2:6">
+      <c r="B20" s="2">
         <v>230006</v>
       </c>
       <c r="C20" s="1">
@@ -1476,18 +1391,14 @@
         <v>100</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F20" s="1">
         <v>100</v>
       </c>
-      <c r="G20" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>230006Name.png</v>
-      </c>
-    </row>
-    <row r="21" spans="2:7">
-      <c r="B21" s="4">
+    </row>
+    <row r="21" spans="2:6">
+      <c r="B21" s="2">
         <v>230007</v>
       </c>
       <c r="C21" s="1">
@@ -1497,18 +1408,14 @@
         <v>100</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F21" s="1">
         <v>100</v>
       </c>
-      <c r="G21" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>230007Name.png</v>
-      </c>
-    </row>
-    <row r="22" spans="2:7">
-      <c r="B22" s="4">
+    </row>
+    <row r="22" spans="2:6">
+      <c r="B22" s="2">
         <v>230008</v>
       </c>
       <c r="C22" s="1">
@@ -1518,18 +1425,14 @@
         <v>100</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F22" s="1">
         <v>100</v>
       </c>
-      <c r="G22" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>230008Name.png</v>
-      </c>
-    </row>
-    <row r="23" spans="2:7">
-      <c r="B23" s="4">
+    </row>
+    <row r="23" spans="2:6">
+      <c r="B23" s="2">
         <v>230009</v>
       </c>
       <c r="C23" s="1">
@@ -1539,18 +1442,14 @@
         <v>100</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F23" s="1">
         <v>100</v>
       </c>
-      <c r="G23" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>230009Name.png</v>
-      </c>
-    </row>
-    <row r="24" spans="2:7">
-      <c r="B24" s="4">
+    </row>
+    <row r="24" spans="2:6">
+      <c r="B24" s="2">
         <v>230010</v>
       </c>
       <c r="C24" s="1">
@@ -1560,18 +1459,14 @@
         <v>100</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F24" s="1">
         <v>100</v>
       </c>
-      <c r="G24" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>230010Name.png</v>
-      </c>
-    </row>
-    <row r="25" spans="2:7">
-      <c r="B25" s="4">
+    </row>
+    <row r="25" spans="2:6">
+      <c r="B25" s="2">
         <v>230011</v>
       </c>
       <c r="C25" s="1">
@@ -1581,18 +1476,14 @@
         <v>100</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F25" s="1">
         <v>100</v>
       </c>
-      <c r="G25" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>230011Name.png</v>
-      </c>
-    </row>
-    <row r="26" spans="2:7">
-      <c r="B26" s="4">
+    </row>
+    <row r="26" spans="2:6">
+      <c r="B26" s="2">
         <v>230012</v>
       </c>
       <c r="C26" s="1">
@@ -1602,18 +1493,14 @@
         <v>100</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F26" s="1">
         <v>100</v>
       </c>
-      <c r="G26" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>230012Name.png</v>
-      </c>
-    </row>
-    <row r="27" spans="2:7">
-      <c r="B27" s="4">
+    </row>
+    <row r="27" spans="2:6">
+      <c r="B27" s="2">
         <v>230013</v>
       </c>
       <c r="C27" s="1">
@@ -1623,18 +1510,14 @@
         <v>100</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F27" s="1">
         <v>100</v>
       </c>
-      <c r="G27" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>230013Name.png</v>
-      </c>
-    </row>
-    <row r="28" spans="2:7">
-      <c r="B28" s="4">
+    </row>
+    <row r="28" spans="2:6">
+      <c r="B28" s="2">
         <v>230014</v>
       </c>
       <c r="C28" s="1">
@@ -1644,18 +1527,14 @@
         <v>100</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F28" s="1">
         <v>100</v>
       </c>
-      <c r="G28" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>230014Name.png</v>
-      </c>
-    </row>
-    <row r="29" spans="2:7">
-      <c r="B29" s="4">
+    </row>
+    <row r="29" spans="2:6">
+      <c r="B29" s="2">
         <v>230015</v>
       </c>
       <c r="C29" s="1">
@@ -1665,18 +1544,14 @@
         <v>100</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F29" s="1">
         <v>100</v>
       </c>
-      <c r="G29" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>230015Name.png</v>
-      </c>
-    </row>
-    <row r="30" spans="2:7">
-      <c r="B30" s="4">
+    </row>
+    <row r="30" spans="2:6">
+      <c r="B30" s="2">
         <v>230016</v>
       </c>
       <c r="C30" s="1">
@@ -1686,18 +1561,14 @@
         <v>100</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F30" s="1">
         <v>100</v>
       </c>
-      <c r="G30" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>230016Name.png</v>
-      </c>
-    </row>
-    <row r="31" spans="2:7">
-      <c r="B31" s="4">
+    </row>
+    <row r="31" spans="2:6">
+      <c r="B31" s="2">
         <v>230017</v>
       </c>
       <c r="C31" s="1">
@@ -1707,18 +1578,14 @@
         <v>100</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F31" s="1">
         <v>100</v>
       </c>
-      <c r="G31" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>230017Name.png</v>
-      </c>
-    </row>
-    <row r="32" spans="2:7">
-      <c r="B32" s="4">
+    </row>
+    <row r="32" spans="2:6">
+      <c r="B32" s="2">
         <v>230018</v>
       </c>
       <c r="C32" s="1">
@@ -1728,18 +1595,14 @@
         <v>100</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F32" s="1">
         <v>100</v>
       </c>
-      <c r="G32" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>230018Name.png</v>
-      </c>
-    </row>
-    <row r="33" spans="2:7">
-      <c r="B33" s="4">
+    </row>
+    <row r="33" spans="2:6">
+      <c r="B33" s="2">
         <v>230019</v>
       </c>
       <c r="C33" s="1">
@@ -1749,18 +1612,14 @@
         <v>100</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F33" s="1">
         <v>100</v>
       </c>
-      <c r="G33" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>230019Name.png</v>
-      </c>
-    </row>
-    <row r="34" spans="2:7">
-      <c r="B34" s="4">
+    </row>
+    <row r="34" spans="2:6">
+      <c r="B34" s="2">
         <v>240000</v>
       </c>
       <c r="C34" s="1">
@@ -1770,18 +1629,14 @@
         <v>100</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F34" s="1">
         <v>100</v>
       </c>
-      <c r="G34" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>240000Name.png</v>
-      </c>
-    </row>
-    <row r="35" spans="2:7">
-      <c r="B35" s="4">
+    </row>
+    <row r="35" spans="2:6">
+      <c r="B35" s="2">
         <v>240001</v>
       </c>
       <c r="C35" s="1">
@@ -1791,18 +1646,14 @@
         <v>100</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F35" s="1">
         <v>100</v>
       </c>
-      <c r="G35" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>240001Name.png</v>
-      </c>
-    </row>
-    <row r="36" spans="2:7">
-      <c r="B36" s="4">
+    </row>
+    <row r="36" spans="2:6">
+      <c r="B36" s="2">
         <v>240002</v>
       </c>
       <c r="C36" s="1">
@@ -1812,18 +1663,14 @@
         <v>100</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F36" s="1">
         <v>100</v>
       </c>
-      <c r="G36" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>240002Name.png</v>
-      </c>
-    </row>
-    <row r="37" spans="2:7">
-      <c r="B37" s="4">
+    </row>
+    <row r="37" spans="2:6">
+      <c r="B37" s="2">
         <v>240003</v>
       </c>
       <c r="C37" s="1">
@@ -1833,18 +1680,14 @@
         <v>100</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F37" s="1">
         <v>100</v>
       </c>
-      <c r="G37" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>240003Name.png</v>
-      </c>
-    </row>
-    <row r="38" spans="2:7">
-      <c r="B38" s="4">
+    </row>
+    <row r="38" spans="2:6">
+      <c r="B38" s="2">
         <v>240004</v>
       </c>
       <c r="C38" s="1">
@@ -1854,18 +1697,14 @@
         <v>100</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F38" s="1">
         <v>100</v>
       </c>
-      <c r="G38" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>240004Name.png</v>
-      </c>
-    </row>
-    <row r="39" spans="2:7">
-      <c r="B39" s="4">
+    </row>
+    <row r="39" spans="2:6">
+      <c r="B39" s="2">
         <v>240005</v>
       </c>
       <c r="C39" s="1">
@@ -1875,18 +1714,14 @@
         <v>100</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F39" s="1">
         <v>100</v>
       </c>
-      <c r="G39" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>240005Name.png</v>
-      </c>
-    </row>
-    <row r="40" spans="2:7">
-      <c r="B40" s="4">
+    </row>
+    <row r="40" spans="2:6">
+      <c r="B40" s="2">
         <v>240006</v>
       </c>
       <c r="C40" s="1">
@@ -1896,18 +1731,14 @@
         <v>100</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F40" s="1">
         <v>100</v>
       </c>
-      <c r="G40" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>240006Name.png</v>
-      </c>
-    </row>
-    <row r="41" spans="2:7">
-      <c r="B41" s="4">
+    </row>
+    <row r="41" spans="2:6">
+      <c r="B41" s="2">
         <v>240007</v>
       </c>
       <c r="C41" s="1">
@@ -1917,18 +1748,14 @@
         <v>100</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F41" s="1">
         <v>100</v>
       </c>
-      <c r="G41" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>240007Name.png</v>
-      </c>
-    </row>
-    <row r="42" spans="2:7">
-      <c r="B42" s="4">
+    </row>
+    <row r="42" spans="2:6">
+      <c r="B42" s="2">
         <v>240008</v>
       </c>
       <c r="C42" s="1">
@@ -1938,18 +1765,14 @@
         <v>100</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F42" s="1">
         <v>100</v>
       </c>
-      <c r="G42" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>240008Name.png</v>
-      </c>
-    </row>
-    <row r="43" spans="2:7">
-      <c r="B43" s="4">
+    </row>
+    <row r="43" spans="2:6">
+      <c r="B43" s="2">
         <v>240009</v>
       </c>
       <c r="C43" s="1">
@@ -1959,18 +1782,14 @@
         <v>100</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F43" s="1">
         <v>100</v>
       </c>
-      <c r="G43" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>240009Name.png</v>
-      </c>
-    </row>
-    <row r="44" spans="2:7">
-      <c r="B44" s="4">
+    </row>
+    <row r="44" spans="2:6">
+      <c r="B44" s="2">
         <v>240010</v>
       </c>
       <c r="C44" s="1">
@@ -1980,18 +1799,14 @@
         <v>100</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F44" s="1">
         <v>100</v>
       </c>
-      <c r="G44" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>240010Name.png</v>
-      </c>
-    </row>
-    <row r="45" spans="2:7">
-      <c r="B45" s="4">
+    </row>
+    <row r="45" spans="2:6">
+      <c r="B45" s="2">
         <v>240011</v>
       </c>
       <c r="C45" s="1">
@@ -2001,18 +1816,14 @@
         <v>100</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F45" s="1">
         <v>100</v>
       </c>
-      <c r="G45" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>240011Name.png</v>
-      </c>
-    </row>
-    <row r="46" spans="2:7">
-      <c r="B46" s="4">
+    </row>
+    <row r="46" spans="2:6">
+      <c r="B46" s="2">
         <v>240012</v>
       </c>
       <c r="C46" s="1">
@@ -2022,18 +1833,14 @@
         <v>100</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F46" s="1">
         <v>100</v>
       </c>
-      <c r="G46" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>240012Name.png</v>
-      </c>
-    </row>
-    <row r="47" spans="2:7">
-      <c r="B47" s="4">
+    </row>
+    <row r="47" spans="2:6">
+      <c r="B47" s="2">
         <v>240013</v>
       </c>
       <c r="C47" s="1">
@@ -2043,18 +1850,14 @@
         <v>100</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F47" s="1">
         <v>100</v>
       </c>
-      <c r="G47" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>240013Name.png</v>
-      </c>
-    </row>
-    <row r="48" spans="2:7">
-      <c r="B48" s="4">
+    </row>
+    <row r="48" spans="2:6">
+      <c r="B48" s="2">
         <v>240014</v>
       </c>
       <c r="C48" s="1">
@@ -2064,18 +1867,14 @@
         <v>100</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F48" s="1">
         <v>100</v>
       </c>
-      <c r="G48" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>240014Name.png</v>
-      </c>
-    </row>
-    <row r="49" spans="2:7">
-      <c r="B49" s="4">
+    </row>
+    <row r="49" spans="2:6">
+      <c r="B49" s="2">
         <v>240015</v>
       </c>
       <c r="C49" s="1">
@@ -2085,18 +1884,14 @@
         <v>100</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F49" s="1">
         <v>100</v>
       </c>
-      <c r="G49" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>240015Name.png</v>
-      </c>
-    </row>
-    <row r="50" spans="2:7">
-      <c r="B50" s="4">
+    </row>
+    <row r="50" spans="2:6">
+      <c r="B50" s="2">
         <v>240016</v>
       </c>
       <c r="C50" s="1">
@@ -2106,18 +1901,14 @@
         <v>100</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F50" s="1">
         <v>100</v>
       </c>
-      <c r="G50" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>240016Name.png</v>
-      </c>
-    </row>
-    <row r="51" spans="2:7">
-      <c r="B51" s="4">
+    </row>
+    <row r="51" spans="2:6">
+      <c r="B51" s="2">
         <v>240017</v>
       </c>
       <c r="C51" s="1">
@@ -2127,18 +1918,14 @@
         <v>100</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F51" s="1">
         <v>100</v>
       </c>
-      <c r="G51" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>240017Name.png</v>
-      </c>
-    </row>
-    <row r="52" spans="2:7">
-      <c r="B52" s="4">
+    </row>
+    <row r="52" spans="2:6">
+      <c r="B52" s="2">
         <v>240018</v>
       </c>
       <c r="C52" s="1">
@@ -2148,18 +1935,14 @@
         <v>100</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F52" s="1">
         <v>100</v>
       </c>
-      <c r="G52" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>240018Name.png</v>
-      </c>
-    </row>
-    <row r="53" spans="2:7">
-      <c r="B53" s="4">
+    </row>
+    <row r="53" spans="2:6">
+      <c r="B53" s="2">
         <v>240019</v>
       </c>
       <c r="C53" s="1">
@@ -2169,14 +1952,10 @@
         <v>100</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F53" s="1">
         <v>100</v>
-      </c>
-      <c r="G53" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>240019Name.png</v>
       </c>
     </row>
   </sheetData>

--- a/ExcelTool/LubanTools/DataTables/Datas/ClothShopData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/ClothShopData.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87768956-FA07-4719-8BC7-6CCEF80023C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView xWindow="3890" yWindow="1530" windowWidth="30580" windowHeight="18680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="布料商店" sheetId="1" r:id="rId1"/>
@@ -65,9 +71,6 @@
     <t>ShopUpdateType</t>
   </si>
   <si>
-    <t>str</t>
-  </si>
-  <si>
     <t>##</t>
   </si>
   <si>
@@ -90,19 +93,17 @@
   </si>
   <si>
     <t>Day</t>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="22">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -114,354 +115,37 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -469,324 +153,35 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="50">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="50">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="常规 2" xfId="49"/>
+    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1044,23 +439,23 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G53"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
-    <col min="3" max="3" width="29.1666666666667" style="1" customWidth="1"/>
-    <col min="4" max="4" width="27.4166666666667" style="1" customWidth="1"/>
-    <col min="5" max="5" width="19.3333333333333" style="1" customWidth="1"/>
+    <col min="3" max="3" width="29.1640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="27.4140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="19.33203125" style="1" customWidth="1"/>
     <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1079,11 +474,11 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -1102,34 +497,34 @@
       <c r="F2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="1" t="s">
+      <c r="B3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B4" s="1">
         <v>220000</v>
       </c>
@@ -1140,17 +535,17 @@
         <v>200</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F4" s="1">
         <v>5</v>
       </c>
       <c r="G4" s="1" t="str">
-        <f t="shared" ref="G4:G53" si="0">CONCATENATE(_xlfn.SINGLE(B:B),"Name.png")</f>
+        <f t="shared" ref="G4:G53" si="0">CONCATENATE(B:B,"Name.png")</f>
         <v>220000Name.png</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B5" s="1">
         <v>220001</v>
       </c>
@@ -1161,7 +556,7 @@
         <v>200</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F5" s="1">
         <v>5</v>
@@ -1171,7 +566,7 @@
         <v>220001Name.png</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B6" s="1">
         <v>220002</v>
       </c>
@@ -1182,7 +577,7 @@
         <v>400</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F6" s="1">
         <v>5</v>
@@ -1192,7 +587,7 @@
         <v>220002Name.png</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B7" s="1">
         <v>220003</v>
       </c>
@@ -1203,7 +598,7 @@
         <v>400</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F7" s="1">
         <v>5</v>
@@ -1213,7 +608,7 @@
         <v>220003Name.png</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B8" s="1">
         <v>220004</v>
       </c>
@@ -1224,7 +619,7 @@
         <v>600</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F8" s="1">
         <v>5</v>
@@ -1234,7 +629,7 @@
         <v>220004Name.png</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B9" s="1">
         <v>220005</v>
       </c>
@@ -1245,7 +640,7 @@
         <v>600</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F9" s="1">
         <v>5</v>
@@ -1255,7 +650,7 @@
         <v>220005Name.png</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B10" s="1">
         <v>220006</v>
       </c>
@@ -1266,7 +661,7 @@
         <v>800</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F10" s="1">
         <v>5</v>
@@ -1276,7 +671,7 @@
         <v>220006Name.png</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B11" s="1">
         <v>220007</v>
       </c>
@@ -1287,7 +682,7 @@
         <v>800</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F11" s="1">
         <v>5</v>
@@ -1297,7 +692,7 @@
         <v>220007Name.png</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B12" s="1">
         <v>220008</v>
       </c>
@@ -1308,7 +703,7 @@
         <v>1000</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F12" s="1">
         <v>5</v>
@@ -1318,7 +713,7 @@
         <v>220008Name.png</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B13" s="1">
         <v>220009</v>
       </c>
@@ -1329,7 +724,7 @@
         <v>1000</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F13" s="1">
         <v>5</v>
@@ -1339,8 +734,8 @@
         <v>220009Name.png</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
-      <c r="B14" s="4">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B14" s="3">
         <v>230000</v>
       </c>
       <c r="C14" s="1">
@@ -1350,7 +745,7 @@
         <v>100</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F14" s="1">
         <v>100</v>
@@ -1360,8 +755,8 @@
         <v>230000Name.png</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
-      <c r="B15" s="4">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B15" s="3">
         <v>230001</v>
       </c>
       <c r="C15" s="1">
@@ -1371,7 +766,7 @@
         <v>100</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F15" s="1">
         <v>100</v>
@@ -1381,8 +776,8 @@
         <v>230001Name.png</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
-      <c r="B16" s="4">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B16" s="3">
         <v>230002</v>
       </c>
       <c r="C16" s="1">
@@ -1392,7 +787,7 @@
         <v>100</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F16" s="1">
         <v>100</v>
@@ -1402,8 +797,8 @@
         <v>230002Name.png</v>
       </c>
     </row>
-    <row r="17" spans="2:7">
-      <c r="B17" s="4">
+    <row r="17" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B17" s="3">
         <v>230003</v>
       </c>
       <c r="C17" s="1">
@@ -1413,7 +808,7 @@
         <v>100</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F17" s="1">
         <v>100</v>
@@ -1423,8 +818,8 @@
         <v>230003Name.png</v>
       </c>
     </row>
-    <row r="18" spans="2:7">
-      <c r="B18" s="4">
+    <row r="18" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B18" s="3">
         <v>230004</v>
       </c>
       <c r="C18" s="1">
@@ -1434,7 +829,7 @@
         <v>100</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F18" s="1">
         <v>100</v>
@@ -1444,8 +839,8 @@
         <v>230004Name.png</v>
       </c>
     </row>
-    <row r="19" spans="2:7">
-      <c r="B19" s="4">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B19" s="3">
         <v>230005</v>
       </c>
       <c r="C19" s="1">
@@ -1455,7 +850,7 @@
         <v>100</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F19" s="1">
         <v>100</v>
@@ -1465,8 +860,8 @@
         <v>230005Name.png</v>
       </c>
     </row>
-    <row r="20" spans="2:7">
-      <c r="B20" s="4">
+    <row r="20" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B20" s="3">
         <v>230006</v>
       </c>
       <c r="C20" s="1">
@@ -1476,7 +871,7 @@
         <v>100</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F20" s="1">
         <v>100</v>
@@ -1486,8 +881,8 @@
         <v>230006Name.png</v>
       </c>
     </row>
-    <row r="21" spans="2:7">
-      <c r="B21" s="4">
+    <row r="21" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B21" s="3">
         <v>230007</v>
       </c>
       <c r="C21" s="1">
@@ -1497,7 +892,7 @@
         <v>100</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F21" s="1">
         <v>100</v>
@@ -1507,8 +902,8 @@
         <v>230007Name.png</v>
       </c>
     </row>
-    <row r="22" spans="2:7">
-      <c r="B22" s="4">
+    <row r="22" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B22" s="3">
         <v>230008</v>
       </c>
       <c r="C22" s="1">
@@ -1518,7 +913,7 @@
         <v>100</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F22" s="1">
         <v>100</v>
@@ -1528,8 +923,8 @@
         <v>230008Name.png</v>
       </c>
     </row>
-    <row r="23" spans="2:7">
-      <c r="B23" s="4">
+    <row r="23" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B23" s="3">
         <v>230009</v>
       </c>
       <c r="C23" s="1">
@@ -1539,7 +934,7 @@
         <v>100</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F23" s="1">
         <v>100</v>
@@ -1549,8 +944,8 @@
         <v>230009Name.png</v>
       </c>
     </row>
-    <row r="24" spans="2:7">
-      <c r="B24" s="4">
+    <row r="24" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B24" s="3">
         <v>230010</v>
       </c>
       <c r="C24" s="1">
@@ -1560,7 +955,7 @@
         <v>100</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F24" s="1">
         <v>100</v>
@@ -1570,8 +965,8 @@
         <v>230010Name.png</v>
       </c>
     </row>
-    <row r="25" spans="2:7">
-      <c r="B25" s="4">
+    <row r="25" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B25" s="3">
         <v>230011</v>
       </c>
       <c r="C25" s="1">
@@ -1581,7 +976,7 @@
         <v>100</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F25" s="1">
         <v>100</v>
@@ -1591,8 +986,8 @@
         <v>230011Name.png</v>
       </c>
     </row>
-    <row r="26" spans="2:7">
-      <c r="B26" s="4">
+    <row r="26" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B26" s="3">
         <v>230012</v>
       </c>
       <c r="C26" s="1">
@@ -1602,7 +997,7 @@
         <v>100</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F26" s="1">
         <v>100</v>
@@ -1612,8 +1007,8 @@
         <v>230012Name.png</v>
       </c>
     </row>
-    <row r="27" spans="2:7">
-      <c r="B27" s="4">
+    <row r="27" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B27" s="3">
         <v>230013</v>
       </c>
       <c r="C27" s="1">
@@ -1623,7 +1018,7 @@
         <v>100</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F27" s="1">
         <v>100</v>
@@ -1633,8 +1028,8 @@
         <v>230013Name.png</v>
       </c>
     </row>
-    <row r="28" spans="2:7">
-      <c r="B28" s="4">
+    <row r="28" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B28" s="3">
         <v>230014</v>
       </c>
       <c r="C28" s="1">
@@ -1644,7 +1039,7 @@
         <v>100</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F28" s="1">
         <v>100</v>
@@ -1654,8 +1049,8 @@
         <v>230014Name.png</v>
       </c>
     </row>
-    <row r="29" spans="2:7">
-      <c r="B29" s="4">
+    <row r="29" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B29" s="3">
         <v>230015</v>
       </c>
       <c r="C29" s="1">
@@ -1665,7 +1060,7 @@
         <v>100</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F29" s="1">
         <v>100</v>
@@ -1675,8 +1070,8 @@
         <v>230015Name.png</v>
       </c>
     </row>
-    <row r="30" spans="2:7">
-      <c r="B30" s="4">
+    <row r="30" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B30" s="3">
         <v>230016</v>
       </c>
       <c r="C30" s="1">
@@ -1686,7 +1081,7 @@
         <v>100</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F30" s="1">
         <v>100</v>
@@ -1696,8 +1091,8 @@
         <v>230016Name.png</v>
       </c>
     </row>
-    <row r="31" spans="2:7">
-      <c r="B31" s="4">
+    <row r="31" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B31" s="3">
         <v>230017</v>
       </c>
       <c r="C31" s="1">
@@ -1707,7 +1102,7 @@
         <v>100</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F31" s="1">
         <v>100</v>
@@ -1717,8 +1112,8 @@
         <v>230017Name.png</v>
       </c>
     </row>
-    <row r="32" spans="2:7">
-      <c r="B32" s="4">
+    <row r="32" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B32" s="3">
         <v>230018</v>
       </c>
       <c r="C32" s="1">
@@ -1728,7 +1123,7 @@
         <v>100</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F32" s="1">
         <v>100</v>
@@ -1738,8 +1133,8 @@
         <v>230018Name.png</v>
       </c>
     </row>
-    <row r="33" spans="2:7">
-      <c r="B33" s="4">
+    <row r="33" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B33" s="3">
         <v>230019</v>
       </c>
       <c r="C33" s="1">
@@ -1749,7 +1144,7 @@
         <v>100</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F33" s="1">
         <v>100</v>
@@ -1759,8 +1154,8 @@
         <v>230019Name.png</v>
       </c>
     </row>
-    <row r="34" spans="2:7">
-      <c r="B34" s="4">
+    <row r="34" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B34" s="3">
         <v>240000</v>
       </c>
       <c r="C34" s="1">
@@ -1770,7 +1165,7 @@
         <v>100</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F34" s="1">
         <v>100</v>
@@ -1780,8 +1175,8 @@
         <v>240000Name.png</v>
       </c>
     </row>
-    <row r="35" spans="2:7">
-      <c r="B35" s="4">
+    <row r="35" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B35" s="3">
         <v>240001</v>
       </c>
       <c r="C35" s="1">
@@ -1791,7 +1186,7 @@
         <v>100</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F35" s="1">
         <v>100</v>
@@ -1801,8 +1196,8 @@
         <v>240001Name.png</v>
       </c>
     </row>
-    <row r="36" spans="2:7">
-      <c r="B36" s="4">
+    <row r="36" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B36" s="3">
         <v>240002</v>
       </c>
       <c r="C36" s="1">
@@ -1812,7 +1207,7 @@
         <v>100</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F36" s="1">
         <v>100</v>
@@ -1822,8 +1217,8 @@
         <v>240002Name.png</v>
       </c>
     </row>
-    <row r="37" spans="2:7">
-      <c r="B37" s="4">
+    <row r="37" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B37" s="3">
         <v>240003</v>
       </c>
       <c r="C37" s="1">
@@ -1833,7 +1228,7 @@
         <v>100</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F37" s="1">
         <v>100</v>
@@ -1843,8 +1238,8 @@
         <v>240003Name.png</v>
       </c>
     </row>
-    <row r="38" spans="2:7">
-      <c r="B38" s="4">
+    <row r="38" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B38" s="3">
         <v>240004</v>
       </c>
       <c r="C38" s="1">
@@ -1854,7 +1249,7 @@
         <v>100</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F38" s="1">
         <v>100</v>
@@ -1864,8 +1259,8 @@
         <v>240004Name.png</v>
       </c>
     </row>
-    <row r="39" spans="2:7">
-      <c r="B39" s="4">
+    <row r="39" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B39" s="3">
         <v>240005</v>
       </c>
       <c r="C39" s="1">
@@ -1875,7 +1270,7 @@
         <v>100</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F39" s="1">
         <v>100</v>
@@ -1885,8 +1280,8 @@
         <v>240005Name.png</v>
       </c>
     </row>
-    <row r="40" spans="2:7">
-      <c r="B40" s="4">
+    <row r="40" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B40" s="3">
         <v>240006</v>
       </c>
       <c r="C40" s="1">
@@ -1896,7 +1291,7 @@
         <v>100</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F40" s="1">
         <v>100</v>
@@ -1906,8 +1301,8 @@
         <v>240006Name.png</v>
       </c>
     </row>
-    <row r="41" spans="2:7">
-      <c r="B41" s="4">
+    <row r="41" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B41" s="3">
         <v>240007</v>
       </c>
       <c r="C41" s="1">
@@ -1917,7 +1312,7 @@
         <v>100</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F41" s="1">
         <v>100</v>
@@ -1927,8 +1322,8 @@
         <v>240007Name.png</v>
       </c>
     </row>
-    <row r="42" spans="2:7">
-      <c r="B42" s="4">
+    <row r="42" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B42" s="3">
         <v>240008</v>
       </c>
       <c r="C42" s="1">
@@ -1938,7 +1333,7 @@
         <v>100</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F42" s="1">
         <v>100</v>
@@ -1948,8 +1343,8 @@
         <v>240008Name.png</v>
       </c>
     </row>
-    <row r="43" spans="2:7">
-      <c r="B43" s="4">
+    <row r="43" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B43" s="3">
         <v>240009</v>
       </c>
       <c r="C43" s="1">
@@ -1959,7 +1354,7 @@
         <v>100</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F43" s="1">
         <v>100</v>
@@ -1969,8 +1364,8 @@
         <v>240009Name.png</v>
       </c>
     </row>
-    <row r="44" spans="2:7">
-      <c r="B44" s="4">
+    <row r="44" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B44" s="3">
         <v>240010</v>
       </c>
       <c r="C44" s="1">
@@ -1980,7 +1375,7 @@
         <v>100</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F44" s="1">
         <v>100</v>
@@ -1990,8 +1385,8 @@
         <v>240010Name.png</v>
       </c>
     </row>
-    <row r="45" spans="2:7">
-      <c r="B45" s="4">
+    <row r="45" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B45" s="3">
         <v>240011</v>
       </c>
       <c r="C45" s="1">
@@ -2001,7 +1396,7 @@
         <v>100</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F45" s="1">
         <v>100</v>
@@ -2011,8 +1406,8 @@
         <v>240011Name.png</v>
       </c>
     </row>
-    <row r="46" spans="2:7">
-      <c r="B46" s="4">
+    <row r="46" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B46" s="3">
         <v>240012</v>
       </c>
       <c r="C46" s="1">
@@ -2022,7 +1417,7 @@
         <v>100</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F46" s="1">
         <v>100</v>
@@ -2032,8 +1427,8 @@
         <v>240012Name.png</v>
       </c>
     </row>
-    <row r="47" spans="2:7">
-      <c r="B47" s="4">
+    <row r="47" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B47" s="3">
         <v>240013</v>
       </c>
       <c r="C47" s="1">
@@ -2043,7 +1438,7 @@
         <v>100</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F47" s="1">
         <v>100</v>
@@ -2053,8 +1448,8 @@
         <v>240013Name.png</v>
       </c>
     </row>
-    <row r="48" spans="2:7">
-      <c r="B48" s="4">
+    <row r="48" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B48" s="3">
         <v>240014</v>
       </c>
       <c r="C48" s="1">
@@ -2064,7 +1459,7 @@
         <v>100</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F48" s="1">
         <v>100</v>
@@ -2074,8 +1469,8 @@
         <v>240014Name.png</v>
       </c>
     </row>
-    <row r="49" spans="2:7">
-      <c r="B49" s="4">
+    <row r="49" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B49" s="3">
         <v>240015</v>
       </c>
       <c r="C49" s="1">
@@ -2085,7 +1480,7 @@
         <v>100</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F49" s="1">
         <v>100</v>
@@ -2095,8 +1490,8 @@
         <v>240015Name.png</v>
       </c>
     </row>
-    <row r="50" spans="2:7">
-      <c r="B50" s="4">
+    <row r="50" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B50" s="3">
         <v>240016</v>
       </c>
       <c r="C50" s="1">
@@ -2106,7 +1501,7 @@
         <v>100</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F50" s="1">
         <v>100</v>
@@ -2116,8 +1511,8 @@
         <v>240016Name.png</v>
       </c>
     </row>
-    <row r="51" spans="2:7">
-      <c r="B51" s="4">
+    <row r="51" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B51" s="3">
         <v>240017</v>
       </c>
       <c r="C51" s="1">
@@ -2127,7 +1522,7 @@
         <v>100</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F51" s="1">
         <v>100</v>
@@ -2137,8 +1532,8 @@
         <v>240017Name.png</v>
       </c>
     </row>
-    <row r="52" spans="2:7">
-      <c r="B52" s="4">
+    <row r="52" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B52" s="3">
         <v>240018</v>
       </c>
       <c r="C52" s="1">
@@ -2148,7 +1543,7 @@
         <v>100</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F52" s="1">
         <v>100</v>
@@ -2158,8 +1553,8 @@
         <v>240018Name.png</v>
       </c>
     </row>
-    <row r="53" spans="2:7">
-      <c r="B53" s="4">
+    <row r="53" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B53" s="3">
         <v>240019</v>
       </c>
       <c r="C53" s="1">
@@ -2169,7 +1564,7 @@
         <v>100</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F53" s="1">
         <v>100</v>
@@ -2180,7 +1575,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>